--- a/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/02_Supervisor_Log.xlsx
+++ b/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/02_Supervisor_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kandilglass20-my.sharepoint.com/personal/ahmed_fergany_kandilglass_com/Documents/Attachments/GitHub/Final_Learning_AI/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_C621BC8FCC9BD56AEC16FA20236E4CEF87855846" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4C52D6A-CC8A-4A87-A712-DF509FC51203}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_C621BC8FCC9BD56AEC16FA20236E4CEF87855846" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8602A5A8-AC38-43F3-8FF1-F18B0FCD01BC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -432,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -458,6 +458,7 @@
     <xf numFmtId="4" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1835,14 +1836,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{270EDBF1-2110-47A6-A964-2F24A26466A3}" name="JobChange_Fact" displayName="JobChange_Fact" ref="A4:R40" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39" totalsRowBorderDxfId="38">
-  <autoFilter ref="A4:R40" xr:uid="{270EDBF1-2110-47A6-A964-2F24A26466A3}">
-    <filterColumn colId="2">
-      <filters>
-        <dateGroupItem year="2026" month="7" day="22" dateTimeGrouping="day"/>
-        <dateGroupItem year="2026" month="7" day="23" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:R40" xr:uid="{270EDBF1-2110-47A6-A964-2F24A26466A3}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{13623D51-A8DA-4FBA-BD30-7BC301050BF2}" name="FactoryCode" dataDxfId="37"/>
     <tableColumn id="2" xr3:uid="{F86F636C-10AC-4EEF-9149-FCEBD8B2BD39}" name="LineNumber" dataDxfId="36"/>
@@ -1870,19 +1864,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07395468-7652-48ED-98AB-8C427A1079DB}" name="DailyProduction_Fact" displayName="DailyProduction_Fact" ref="A4:O144" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A4:O144" xr:uid="{07395468-7652-48ED-98AB-8C427A1079DB}">
-    <filterColumn colId="1">
-      <filters>
-        <dateGroupItem year="2026" month="7" day="15" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="4">
       <filters>
         <filter val="21"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="5">
-      <filters>
-        <filter val="ORD-2026-00160"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2269,48 +2253,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -2373,7 +2357,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>29</v>
       </c>
@@ -2427,7 +2411,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>29</v>
       </c>
@@ -2479,7 +2463,7 @@
       </c>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>29</v>
       </c>
@@ -2535,7 +2519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>29</v>
       </c>
@@ -2591,7 +2575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>29</v>
       </c>
@@ -2647,7 +2631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>29</v>
       </c>
@@ -2703,7 +2687,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>29</v>
       </c>
@@ -2759,7 +2743,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>29</v>
       </c>
@@ -2813,7 +2797,7 @@
       </c>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>29</v>
       </c>
@@ -2869,7 +2853,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>29</v>
       </c>
@@ -2925,7 +2909,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>29</v>
       </c>
@@ -2977,7 +2961,7 @@
       </c>
       <c r="R15" s="14"/>
     </row>
-    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>29</v>
       </c>
@@ -3031,7 +3015,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>29</v>
       </c>
@@ -3087,7 +3071,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>29</v>
       </c>
@@ -3141,7 +3125,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>29</v>
       </c>
@@ -3195,7 +3179,7 @@
       </c>
       <c r="R19" s="14"/>
     </row>
-    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>29</v>
       </c>
@@ -3249,7 +3233,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>29</v>
       </c>
@@ -3305,7 +3289,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>29</v>
       </c>
@@ -3361,7 +3345,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>29</v>
       </c>
@@ -3417,7 +3401,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>29</v>
       </c>
@@ -3473,7 +3457,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>29</v>
       </c>
@@ -3527,7 +3511,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>29</v>
       </c>
@@ -3583,7 +3567,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>29</v>
       </c>
@@ -3639,7 +3623,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>29</v>
       </c>
@@ -4021,7 +4005,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>29</v>
       </c>
@@ -4075,7 +4059,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>29</v>
       </c>
@@ -4131,7 +4115,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>29</v>
       </c>
@@ -4185,7 +4169,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>29</v>
       </c>
@@ -4239,7 +4223,7 @@
       </c>
       <c r="R38" s="14"/>
     </row>
-    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>29</v>
       </c>
@@ -4295,7 +4279,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>29</v>
       </c>
@@ -4582,10 +4566,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O559"/>
+  <dimension ref="A1:P559"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
@@ -4602,50 +4586,50 @@
     <col min="15" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-    </row>
-    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+    </row>
+    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -4692,7 +4676,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>29</v>
       </c>
@@ -4738,13 +4722,17 @@
       <c r="O5" s="18">
         <v>1119</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="13">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>52</v>
@@ -4756,7 +4744,7 @@
         <v>21</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>51</v>
@@ -4785,8 +4773,12 @@
       <c r="O6" s="18">
         <v>454</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>29</v>
       </c>
@@ -4832,8 +4824,12 @@
       <c r="O7" s="18">
         <v>455</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>29</v>
       </c>
@@ -4879,8 +4875,12 @@
       <c r="O8" s="18">
         <v>1158</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>29</v>
       </c>
@@ -4926,8 +4926,12 @@
       <c r="O9" s="18">
         <v>934</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>29</v>
       </c>
@@ -4973,8 +4977,12 @@
       <c r="O10" s="18">
         <v>1239</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>29</v>
       </c>
@@ -5018,10 +5026,14 @@
         <v>32374</v>
       </c>
       <c r="O11" s="18">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="P11" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>29</v>
       </c>
@@ -5067,8 +5079,12 @@
       <c r="O12" s="18">
         <v>775</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>734</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>29</v>
       </c>
@@ -5114,8 +5130,12 @@
       <c r="O13" s="18">
         <v>439</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>29</v>
       </c>
@@ -5161,8 +5181,12 @@
       <c r="O14" s="18">
         <v>561</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P14" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>676</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>29</v>
       </c>
@@ -5208,8 +5232,12 @@
       <c r="O15" s="18">
         <v>1116</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P15" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>29</v>
       </c>
@@ -5229,7 +5257,7 @@
         <v>32</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="H16" s="18">
         <v>8</v>
@@ -5255,8 +5283,12 @@
       <c r="O16" s="18">
         <v>1962</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>857</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>29</v>
       </c>
@@ -5302,8 +5334,12 @@
       <c r="O17" s="18">
         <v>1275</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P17" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>29</v>
       </c>
@@ -5349,8 +5385,12 @@
       <c r="O18" s="18">
         <v>371</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P18" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>29</v>
       </c>
@@ -5396,8 +5436,12 @@
       <c r="O19" s="18">
         <v>822</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P19" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>29</v>
       </c>
@@ -5443,8 +5487,12 @@
       <c r="O20" s="18">
         <v>644</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P20" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>29</v>
       </c>
@@ -5490,8 +5538,12 @@
       <c r="O21" s="18">
         <v>702</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>29</v>
       </c>
@@ -5537,8 +5589,12 @@
       <c r="O22" s="18">
         <v>794</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>29</v>
       </c>
@@ -5584,8 +5640,12 @@
       <c r="O23" s="18">
         <v>1652</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>29</v>
       </c>
@@ -5631,8 +5691,12 @@
       <c r="O24" s="18">
         <v>462</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>808</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>29</v>
       </c>
@@ -5652,7 +5716,7 @@
         <v>68</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="H25" s="18">
         <v>12</v>
@@ -5678,8 +5742,12 @@
       <c r="O25" s="18">
         <v>311</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>29</v>
       </c>
@@ -5725,8 +5793,12 @@
       <c r="O26" s="18">
         <v>685</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>651</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>29</v>
       </c>
@@ -5772,8 +5844,12 @@
       <c r="O27" s="18">
         <v>439</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>29</v>
       </c>
@@ -5819,8 +5895,12 @@
       <c r="O28" s="18">
         <v>543</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>29</v>
       </c>
@@ -5866,8 +5946,12 @@
       <c r="O29" s="18">
         <v>820</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P29" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>29</v>
       </c>
@@ -5913,8 +5997,12 @@
       <c r="O30" s="18">
         <v>1901</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P30" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>819</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>29</v>
       </c>
@@ -5960,8 +6048,12 @@
       <c r="O31" s="18">
         <v>1821</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P31" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>29</v>
       </c>
@@ -6007,8 +6099,12 @@
       <c r="O32" s="18">
         <v>310</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P32" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>29</v>
       </c>
@@ -6054,8 +6150,12 @@
       <c r="O33" s="18">
         <v>509</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P33" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>29</v>
       </c>
@@ -6101,8 +6201,12 @@
       <c r="O34" s="18">
         <v>341</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P34" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>29</v>
       </c>
@@ -6148,8 +6252,12 @@
       <c r="O35" s="18">
         <v>873</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P35" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>29</v>
       </c>
@@ -6195,8 +6303,12 @@
       <c r="O36" s="18">
         <v>927</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P36" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>29</v>
       </c>
@@ -6242,8 +6354,12 @@
       <c r="O37" s="18">
         <v>1556</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P37" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>29</v>
       </c>
@@ -6289,8 +6405,12 @@
       <c r="O38" s="18">
         <v>286</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P38" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>713</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>29</v>
       </c>
@@ -6336,8 +6456,12 @@
       <c r="O39" s="18">
         <v>1788</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P39" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>29</v>
       </c>
@@ -6383,8 +6507,12 @@
       <c r="O40" s="18">
         <v>851</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P40" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-266</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>29</v>
       </c>
@@ -6430,8 +6558,12 @@
       <c r="O41" s="18">
         <v>590</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P41" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>744</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>29</v>
       </c>
@@ -6477,8 +6609,12 @@
       <c r="O42" s="18">
         <v>1562</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P42" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>29</v>
       </c>
@@ -6524,8 +6660,12 @@
       <c r="O43" s="18">
         <v>488</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P43" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>29</v>
       </c>
@@ -6571,8 +6711,12 @@
       <c r="O44" s="18">
         <v>158</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P44" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>830</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>29</v>
       </c>
@@ -6592,7 +6736,7 @@
         <v>53</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="H45" s="18">
         <v>10</v>
@@ -6618,8 +6762,12 @@
       <c r="O45" s="18">
         <v>204</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P45" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>29</v>
       </c>
@@ -6665,8 +6813,12 @@
       <c r="O46" s="18">
         <v>506</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P46" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>29</v>
       </c>
@@ -6712,8 +6864,12 @@
       <c r="O47" s="18">
         <v>811</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P47" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>955</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>29</v>
       </c>
@@ -6759,8 +6915,12 @@
       <c r="O48" s="18">
         <v>527</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P48" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>29</v>
       </c>
@@ -6806,8 +6966,12 @@
       <c r="O49" s="18">
         <v>620</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P49" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>29</v>
       </c>
@@ -6853,8 +7017,12 @@
       <c r="O50" s="18">
         <v>304</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P50" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>29</v>
       </c>
@@ -6900,8 +7068,12 @@
       <c r="O51" s="18">
         <v>1706</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>29</v>
       </c>
@@ -6947,8 +7119,12 @@
       <c r="O52" s="18">
         <v>998</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P52" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>29</v>
       </c>
@@ -6994,8 +7170,12 @@
       <c r="O53" s="18">
         <v>606</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P53" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>29</v>
       </c>
@@ -7041,8 +7221,12 @@
       <c r="O54" s="18">
         <v>894</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P54" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>29</v>
       </c>
@@ -7088,8 +7272,12 @@
       <c r="O55" s="18">
         <v>683</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P55" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>29</v>
       </c>
@@ -7135,8 +7323,12 @@
       <c r="O56" s="18">
         <v>1764</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P56" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>802</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>29</v>
       </c>
@@ -7182,8 +7374,12 @@
       <c r="O57" s="18">
         <v>830</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P57" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>29</v>
       </c>
@@ -7229,8 +7425,12 @@
       <c r="O58" s="18">
         <v>1989</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P58" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-1029</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>29</v>
       </c>
@@ -7276,8 +7476,12 @@
       <c r="O59" s="18">
         <v>723</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P59" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>782</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>29</v>
       </c>
@@ -7323,8 +7527,12 @@
       <c r="O60" s="18">
         <v>532</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P60" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>29</v>
       </c>
@@ -7370,8 +7578,12 @@
       <c r="O61" s="18">
         <v>367</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P61" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>29</v>
       </c>
@@ -7417,8 +7629,12 @@
       <c r="O62" s="18">
         <v>266</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P62" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>29</v>
       </c>
@@ -7464,8 +7680,12 @@
       <c r="O63" s="18">
         <v>901</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P63" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>983</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>29</v>
       </c>
@@ -7511,8 +7731,12 @@
       <c r="O64" s="18">
         <v>1128</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P64" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-207</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>29</v>
       </c>
@@ -7558,8 +7782,12 @@
       <c r="O65" s="18">
         <v>534</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P65" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>29</v>
       </c>
@@ -7605,8 +7833,12 @@
       <c r="O66" s="18">
         <v>565</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P66" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>29</v>
       </c>
@@ -7652,8 +7884,12 @@
       <c r="O67" s="18">
         <v>589</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P67" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>29</v>
       </c>
@@ -7699,8 +7935,12 @@
       <c r="O68" s="18">
         <v>286</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P68" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>29</v>
       </c>
@@ -7746,8 +7986,12 @@
       <c r="O69" s="18">
         <v>257</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P69" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>29</v>
       </c>
@@ -7793,8 +8037,12 @@
       <c r="O70" s="18">
         <v>737</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P70" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>29</v>
       </c>
@@ -7840,8 +8088,12 @@
       <c r="O71" s="18">
         <v>1080</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P71" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>865</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>29</v>
       </c>
@@ -7887,8 +8139,12 @@
       <c r="O72" s="18">
         <v>585</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P72" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>29</v>
       </c>
@@ -7934,8 +8190,12 @@
       <c r="O73" s="18">
         <v>578</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P73" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-355</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>29</v>
       </c>
@@ -7981,8 +8241,12 @@
       <c r="O74" s="18">
         <v>414</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P74" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
         <v>29</v>
       </c>
@@ -8028,8 +8292,12 @@
       <c r="O75" s="18">
         <v>1320</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P75" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>29</v>
       </c>
@@ -8075,8 +8343,12 @@
       <c r="O76" s="18">
         <v>449</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P76" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>29</v>
       </c>
@@ -8122,8 +8394,12 @@
       <c r="O77" s="18">
         <v>1063</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P77" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>928</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>29</v>
       </c>
@@ -8169,8 +8445,12 @@
       <c r="O78" s="18">
         <v>682</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P78" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>828</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
         <v>29</v>
       </c>
@@ -8216,8 +8496,12 @@
       <c r="O79" s="18">
         <v>164</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P79" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
         <v>29</v>
       </c>
@@ -8263,8 +8547,12 @@
       <c r="O80" s="18">
         <v>484</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P80" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>29</v>
       </c>
@@ -8310,8 +8598,12 @@
       <c r="O81" s="18">
         <v>457</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P81" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>734</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>29</v>
       </c>
@@ -8357,8 +8649,12 @@
       <c r="O82" s="18">
         <v>545</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P82" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
         <v>29</v>
       </c>
@@ -8404,8 +8700,12 @@
       <c r="O83" s="18">
         <v>1442</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P83" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>29</v>
       </c>
@@ -8451,8 +8751,12 @@
       <c r="O84" s="18">
         <v>375</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P84" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
         <v>29</v>
       </c>
@@ -8498,8 +8802,12 @@
       <c r="O85" s="18">
         <v>974</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P85" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
         <v>29</v>
       </c>
@@ -8545,8 +8853,12 @@
       <c r="O86" s="18">
         <v>531</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P86" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
         <v>29</v>
       </c>
@@ -8592,8 +8904,12 @@
       <c r="O87" s="18">
         <v>393</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P87" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
         <v>29</v>
       </c>
@@ -8639,8 +8955,12 @@
       <c r="O88" s="18">
         <v>953</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P88" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
         <v>29</v>
       </c>
@@ -8686,8 +9006,12 @@
       <c r="O89" s="18">
         <v>1363</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P89" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
         <v>29</v>
       </c>
@@ -8733,8 +9057,12 @@
       <c r="O90" s="18">
         <v>528</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P90" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>774</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
         <v>29</v>
       </c>
@@ -8780,8 +9108,12 @@
       <c r="O91" s="18">
         <v>265</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P91" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
         <v>29</v>
       </c>
@@ -8827,8 +9159,12 @@
       <c r="O92" s="18">
         <v>1023</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P92" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>659</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>29</v>
       </c>
@@ -8874,8 +9210,12 @@
       <c r="O93" s="18">
         <v>1160</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P93" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
         <v>29</v>
       </c>
@@ -8921,8 +9261,12 @@
       <c r="O94" s="18">
         <v>1198</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P94" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>29</v>
       </c>
@@ -8942,7 +9286,7 @@
         <v>33</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="H95" s="18">
         <v>12</v>
@@ -8968,8 +9312,12 @@
       <c r="O95" s="18">
         <v>1297</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P95" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>29</v>
       </c>
@@ -9015,8 +9363,12 @@
       <c r="O96" s="18">
         <v>936</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P96" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-207</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>29</v>
       </c>
@@ -9062,8 +9414,12 @@
       <c r="O97" s="18">
         <v>435</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P97" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
         <v>29</v>
       </c>
@@ -9109,8 +9465,12 @@
       <c r="O98" s="18">
         <v>301</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P98" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
         <v>29</v>
       </c>
@@ -9156,8 +9516,12 @@
       <c r="O99" s="18">
         <v>571</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P99" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-208</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
         <v>29</v>
       </c>
@@ -9203,8 +9567,12 @@
       <c r="O100" s="18">
         <v>1310</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P100" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
         <v>29</v>
       </c>
@@ -9250,8 +9618,12 @@
       <c r="O101" s="18">
         <v>1311</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P101" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
         <v>29</v>
       </c>
@@ -9297,8 +9669,12 @@
       <c r="O102" s="18">
         <v>817</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P102" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
         <v>29</v>
       </c>
@@ -9344,8 +9720,12 @@
       <c r="O103" s="18">
         <v>1561</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P103" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
         <v>29</v>
       </c>
@@ -9391,8 +9771,12 @@
       <c r="O104" s="18">
         <v>892</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P104" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
         <v>29</v>
       </c>
@@ -9438,8 +9822,12 @@
       <c r="O105" s="18">
         <v>411</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P105" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
         <v>29</v>
       </c>
@@ -9485,8 +9873,12 @@
       <c r="O106" s="18">
         <v>1476</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P106" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
         <v>29</v>
       </c>
@@ -9532,8 +9924,12 @@
       <c r="O107" s="18">
         <v>935</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P107" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
         <v>29</v>
       </c>
@@ -9579,8 +9975,12 @@
       <c r="O108" s="18">
         <v>1249</v>
       </c>
-    </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P108" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
         <v>29</v>
       </c>
@@ -9626,8 +10026,12 @@
       <c r="O109" s="18">
         <v>704</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P109" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
         <v>29</v>
       </c>
@@ -9673,8 +10077,12 @@
       <c r="O110" s="18">
         <v>609</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P110" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
         <v>29</v>
       </c>
@@ -9720,8 +10128,12 @@
       <c r="O111" s="18">
         <v>688</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P111" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>770</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
         <v>29</v>
       </c>
@@ -9767,8 +10179,12 @@
       <c r="O112" s="18">
         <v>544</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P112" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-119</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
         <v>29</v>
       </c>
@@ -9814,8 +10230,12 @@
       <c r="O113" s="18">
         <v>594</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P113" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
         <v>29</v>
       </c>
@@ -9861,8 +10281,12 @@
       <c r="O114" s="18">
         <v>641</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P114" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-88</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
         <v>29</v>
       </c>
@@ -9908,8 +10332,12 @@
       <c r="O115" s="18">
         <v>839</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P115" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-343</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
         <v>29</v>
       </c>
@@ -9955,8 +10383,12 @@
       <c r="O116" s="18">
         <v>585</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P116" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
         <v>29</v>
       </c>
@@ -10002,8 +10434,12 @@
       <c r="O117" s="18">
         <v>960</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P117" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
         <v>29</v>
       </c>
@@ -10049,8 +10485,12 @@
       <c r="O118" s="18">
         <v>851</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P118" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>29</v>
       </c>
@@ -10096,8 +10536,12 @@
       <c r="O119" s="18">
         <v>298</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P119" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
         <v>29</v>
       </c>
@@ -10143,8 +10587,12 @@
       <c r="O120" s="18">
         <v>716</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P120" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>-137</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>29</v>
       </c>
@@ -10190,8 +10638,12 @@
       <c r="O121" s="18">
         <v>291</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P121" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
         <v>29</v>
       </c>
@@ -10237,8 +10689,12 @@
       <c r="O122" s="18">
         <v>535</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P122" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>958</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>29</v>
       </c>
@@ -10284,8 +10740,12 @@
       <c r="O123" s="18">
         <v>425</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P123" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3371</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
         <v>29</v>
       </c>
@@ -10331,8 +10791,12 @@
       <c r="O124" s="18">
         <v>966</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P124" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
         <v>29</v>
       </c>
@@ -10378,8 +10842,12 @@
       <c r="O125" s="18">
         <v>2146</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P125" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3726</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
         <v>29</v>
       </c>
@@ -10425,8 +10893,12 @@
       <c r="O126" s="18">
         <v>648</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P126" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>846</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
         <v>29</v>
       </c>
@@ -10472,8 +10944,12 @@
       <c r="O127" s="18">
         <v>296</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P127" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
         <v>29</v>
       </c>
@@ -10519,8 +10995,12 @@
       <c r="O128" s="18">
         <v>708</v>
       </c>
-    </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P128" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
         <v>29</v>
       </c>
@@ -10566,8 +11046,12 @@
       <c r="O129" s="18">
         <v>295</v>
       </c>
-    </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P129" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
         <v>29</v>
       </c>
@@ -10613,8 +11097,12 @@
       <c r="O130" s="18">
         <v>875</v>
       </c>
-    </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P130" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3328</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
         <v>29</v>
       </c>
@@ -10660,8 +11148,12 @@
       <c r="O131" s="18">
         <v>1570</v>
       </c>
-    </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P131" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
         <v>29</v>
       </c>
@@ -10707,8 +11199,12 @@
       <c r="O132" s="18">
         <v>785</v>
       </c>
-    </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P132" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
         <v>29</v>
       </c>
@@ -10754,8 +11250,12 @@
       <c r="O133" s="18">
         <v>1480</v>
       </c>
-    </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P133" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
         <v>29</v>
       </c>
@@ -10801,8 +11301,12 @@
       <c r="O134" s="18">
         <v>1583</v>
       </c>
-    </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P134" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
         <v>29</v>
       </c>
@@ -10848,8 +11352,12 @@
       <c r="O135" s="18">
         <v>722</v>
       </c>
-    </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P135" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
         <v>29</v>
       </c>
@@ -10869,7 +11377,7 @@
         <v>62</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="H136" s="18">
         <v>12</v>
@@ -10895,8 +11403,12 @@
       <c r="O136" s="18">
         <v>947</v>
       </c>
-    </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P136" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
         <v>29</v>
       </c>
@@ -10942,8 +11454,12 @@
       <c r="O137" s="18">
         <v>419</v>
       </c>
-    </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P137" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>642</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
         <v>29</v>
       </c>
@@ -10989,8 +11505,12 @@
       <c r="O138" s="18">
         <v>1101</v>
       </c>
-    </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P138" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
         <v>29</v>
       </c>
@@ -11036,8 +11556,12 @@
       <c r="O139" s="18">
         <v>925</v>
       </c>
-    </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P139" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
         <v>29</v>
       </c>
@@ -11083,8 +11607,12 @@
       <c r="O140" s="18">
         <v>426</v>
       </c>
-    </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P140" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>962</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
         <v>29</v>
       </c>
@@ -11130,8 +11658,12 @@
       <c r="O141" s="18">
         <v>1904</v>
       </c>
-    </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P141" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
         <v>29</v>
       </c>
@@ -11177,8 +11709,12 @@
       <c r="O142" s="18">
         <v>329</v>
       </c>
-    </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P142" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
         <v>29</v>
       </c>
@@ -11224,8 +11760,12 @@
       <c r="O143" s="18">
         <v>519</v>
       </c>
-    </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P143" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
         <v>29</v>
       </c>
@@ -11270,6 +11810,10 @@
       </c>
       <c r="O144" s="18">
         <v>486</v>
+      </c>
+      <c r="P144" s="19">
+        <f>DailyProduction_Fact[[#This Row],[DesignOutput]]-DailyProduction_Fact[[#This Row],[ActualPack]]-DailyProduction_Fact[[#This Row],[TotalHold]]</f>
+        <v>1963</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
